--- a/data/trans_dic/IP31KM04_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,49; 57,08</t>
+          <t>46,13; 67,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,94; 67,64</t>
+          <t>37,44; 58,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,92; 59,36</t>
+          <t>44,31; 60,24</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,27; 53,03</t>
+          <t>46,95; 59,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,77; 58,96</t>
+          <t>40,89; 54,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,47; 54,96</t>
+          <t>46,27; 55,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,02; 57,55</t>
+          <t>40,23; 53,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,54; 52,78</t>
+          <t>42,46; 55,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,69; 51,84</t>
+          <t>43,18; 52,39</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,46; 41,8</t>
+          <t>36,02; 49,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,4; 50,33</t>
+          <t>34,69; 45,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,72; 43,96</t>
+          <t>36,51; 45,69</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,04; 46,6</t>
+          <t>43,48; 50,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,44; 50,23</t>
+          <t>41,2; 48,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,45; 47,45</t>
+          <t>43,27; 48,28</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21422</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>20469</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>41891</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16503; 26539</t>
+          <t>17267; 25143</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20353; 30630</t>
+          <t>15981; 25177</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39388; 54482</t>
+          <t>35502; 48261</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73863</t>
+          <t>84329</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>96228</t>
+          <t>69347</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170092</t>
+          <t>153676</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64155; 84480</t>
+          <t>73723; 93717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85095; 107289</t>
+          <t>59506; 78780</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155185; 187558</t>
+          <t>139991; 167922</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86335</t>
+          <t>93033</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97769</t>
+          <t>85275</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184105</t>
+          <t>178308</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76180; 99606</t>
+          <t>80518; 106238</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84023; 112146</t>
+          <t>74164; 96646</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>164602; 199879</t>
+          <t>161839; 196366</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>132</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>96389</t>
+          <t>121514</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>127066</t>
+          <t>101499</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223455</t>
+          <t>223013</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67095; 114638</t>
+          <t>105256; 143189</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107965; 153502</t>
+          <t>88574; 116434</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>189515; 254655</t>
+          <t>199903; 250171</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>408</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>278064</t>
+          <t>320299</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276591</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>624578</t>
+          <t>596889</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>241923; 304384</t>
+          <t>298651; 346673</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316080; 374094</t>
+          <t>254684; 298384</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>579463; 663286</t>
+          <t>564640; 630113</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM04_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>57,23%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47,96%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>52,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>46,13; 67,16</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37,44; 58,99</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44,31; 60,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>53,7%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47,66%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>50,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>46,95; 59,68</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40,89; 54,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>46,27; 55,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>46,49%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>48,82%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>40,23; 53,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>42,46; 55,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>43,18; 52,39</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>41,58%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>39,75%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>36,02; 49,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>34,69; 45,6</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36,51; 45,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>45,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>43,48; 50,47</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41,2; 48,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43,27; 48,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.57225746629941</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4795762833680734</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5228827133753087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>21422</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>20469</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41891</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4612596339118872</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3744308858776975</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4431363827818428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>17267; 25143</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15981; 25177</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>35502; 48261</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6716412218080192</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.589880672333145</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6023831019808312</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5369816364644965</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4765551410893439</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5079191992271606</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>84329</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>69347</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>153676</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4694502203748462</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4089222820001205</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4626879091498934</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>73723; 93717</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>59506; 78780</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>139991; 167922</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5967609104509174</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5413734346689165</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5550028767671263</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4648726906823658</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4882022796054725</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4757452974721892</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>93033</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>85275</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>178308</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4023359019469075</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4245914161292154</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.4318022793477557</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>80518; 106238</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>74164; 96646</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>161839; 196366</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5308562108344009</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5532977711652036</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5239236027982616</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.415830033234642</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3975108761234232</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4072874468344558</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>121514</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>101499</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>223013</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.3601924263882872</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.3468904065495694</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.365081556711127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>105256; 143189</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>88574; 116434</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>199903; 250171</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4900036211494522</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4560008501669408</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.456884238114017</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4663473195374052</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4474070725283274</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.4573751166400384</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>320299</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>276591</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>596889</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.4348287894640795</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4119714322322891</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4326639482468276</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>298651; 346673</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>254684; 298384</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>564640; 630113</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5047485719750419</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4826592264567426</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.482833925059578</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>21422</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>20469</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>41891</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>17267</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>15981</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>35502</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>25143</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>25177</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>48261</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>84329</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>69347</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>153676</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>73723</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>59506</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>139991</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>93717</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>78780</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>167922</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>93033</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>85275</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>178308</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>80518</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>74164</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>161839</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>106238</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>96646</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>196366</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>121514</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>101499</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>223013</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>105256</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>88574</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>199903</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>143189</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>116434</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>250171</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>437</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>320299</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>276591</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>596889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>298651</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>254684</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>564640</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>346673</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>298384</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>630113</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>